--- a/data/trans_orig/Q20C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007 (tasa de respuesta: 96,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -846,97 +846,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1534</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>40,61%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>872</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4749</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3606</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,62 +994,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1610</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1585</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4068</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>45,09%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>989</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4082</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4033</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>45,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5073</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012 (tasa de respuesta: 97,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>44475</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>63987</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016 (tasa de respuesta: 92,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,1%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,62 +7717,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7292</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6843</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>809</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023 (tasa de respuesta: 93,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>50185</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14048</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18557</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44475</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>40272</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,82 +7241,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>40,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8049</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>34,98%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>62,53%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>7440</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>12981</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>42,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4503</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8537</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>66,32%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>7440</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>3411</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>13229</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24998</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>467</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,67 +10789,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>1159</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3752</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>3058</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21617</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21617</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21617</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24649</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>29084</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>41556</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>35425</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>55003</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
